--- a/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-17.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-17.xlsx
@@ -2987,12 +2987,12 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>11.05 – 12.94</t>
+          <t>10.80 – 13.19</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>12.00 ± 0.95</t>
+          <t>12.00 ± 1.20</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9523,10 +9523,26 @@
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="3" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr"/>
-      <c r="M82" s="3" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>WED_THC26 : CBD1</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>23.40 – 28.59</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>26.00 ± 2.60</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>25.15</t>
@@ -12489,12 +12505,12 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>11.05 – 12.94</t>
+          <t>10.80 – 13.19</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>12.00 ± 0.95</t>
+          <t>12.00 ± 1.20</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -19384,10 +19400,26 @@
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>WED_THC26 : CBD1</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>23.40 – 28.59</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>26.00 ± 2.60</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>25.15</t>

--- a/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-17.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-17.xlsx
@@ -9522,7 +9522,11 @@
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>HYBRID · THC · MACHINE TRIMMED (TO BE DETERMINED)</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Grade I</t>
@@ -19399,7 +19403,11 @@
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>HYBRID · THC · MACHINE TRIMMED (TO BE DETERMINED)</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Grade I</t>

--- a/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-17.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-17.xlsx
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
